--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T05:36:05+00:00</t>
+    <t>2026-07-29T08:04:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -522,8 +522,7 @@
     <t>Observation.moodCode</t>
   </si>
   <si>
-    <t xml:space="preserve">
- - Si la demande fait partie d'un plan de soins : @moodCode='INT'  
+    <t>- Si la demande fait partie d'un plan de soins : @moodCode='INT'  
  - Si la demande est une proposition : @moodCode='PRP'  
  - Si la demande est un objectif à atteindre : @moodCode='GOL'</t>
   </si>
@@ -556,13 +555,13 @@
     <t>Observation.code</t>
   </si>
   <si>
-    <t xml:space="preserve">Type de la demande.
+    <t>Type de la demande.
  -  Si aucun code n'est trouvé dans des terminologies existantes, utiliser le code : 
  @code='GEN-092.04.20'
  @displayName='Autre demande d’examen ou de suivi'
  @codeSystem='1.2.250.1.213.1.1.4.322' 
  @codeSystemName='TerminologieCISIS'  
- et décrire le type de la demande sous forme de texte libre dans la partie narrative avec une référence vers l'entrée correspondante. </t>
+ et décrire le type de la demande sous forme de texte libre dans la partie narrative avec une référence vers l'entrée correspondante.</t>
   </si>
   <si>
     <t>Type de la demande</t>
@@ -890,7 +889,7 @@
     <t>Observation.languageCode</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/all-languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Observation.value</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:04:35+00:00</t>
+    <t>2026-07-29T08:58:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:58:09+00:00</t>
+    <t>2026-07-29T09:37:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:37:21+00:00</t>
+    <t>2026-08-03T10:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
